--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\77369\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BaiduSyncdisk\弘泽工贸 黄奇品\amazon-profit-calculator-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53D55A6-2223-4B29-B03D-7793292AC98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7585F9-5734-4AA6-996B-ED5B1D2600EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="2655" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="3510" windowWidth="26715" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Columns" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="343">
   <si>
     <t>Original</t>
   </si>
@@ -829,6 +829,247 @@
   </si>
   <si>
     <t>versand durch amazon lagergebühr - umkehrung</t>
+  </si>
+  <si>
+    <t>debt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负余额/信用卡扣费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fba removal fee</t>
+  </si>
+  <si>
+    <t>FBA弃置费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>トランザクションの種類</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>広告費用</t>
+  </si>
+  <si>
+    <t>日付/時間</t>
+  </si>
+  <si>
+    <t>決済番号</t>
+  </si>
+  <si>
+    <t>注文番号</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>Amazon 出品サービス</t>
+  </si>
+  <si>
+    <t>フルフィルメント</t>
+  </si>
+  <si>
+    <t>市町村</t>
+  </si>
+  <si>
+    <t>都道府県</t>
+  </si>
+  <si>
+    <t>郵便番号</t>
+  </si>
+  <si>
+    <t>商品売上</t>
+  </si>
+  <si>
+    <t>配送料</t>
+  </si>
+  <si>
+    <t>ギフト包装手数料</t>
+  </si>
+  <si>
+    <t>プロモーション割引額</t>
+  </si>
+  <si>
+    <t>手数料</t>
+  </si>
+  <si>
+    <t>FBA 手数料</t>
+  </si>
+  <si>
+    <t>Amazonポイントの費用</t>
+  </si>
+  <si>
+    <t>トランザクションに関するその他の手数料</t>
+  </si>
+  <si>
+    <t>その他</t>
+  </si>
+  <si>
+    <t>合計</t>
+  </si>
+  <si>
+    <t>settlement id</t>
+  </si>
+  <si>
+    <t>order id</t>
+  </si>
+  <si>
+    <t>marketplace</t>
+  </si>
+  <si>
+    <t>fulfillment</t>
+  </si>
+  <si>
+    <t>order city</t>
+  </si>
+  <si>
+    <t>order state</t>
+  </si>
+  <si>
+    <t>order postal</t>
+  </si>
+  <si>
+    <t>shipping credits</t>
+  </si>
+  <si>
+    <t>gift wrap credits</t>
+  </si>
+  <si>
+    <t>promotional rebates</t>
+  </si>
+  <si>
+    <t>selling fees</t>
+  </si>
+  <si>
+    <t>fba fees</t>
+  </si>
+  <si>
+    <t>points fees</t>
+  </si>
+  <si>
+    <t>other transaction fees</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>SellerPayments_Report_Fee_Subscription</t>
+  </si>
+  <si>
+    <t>FBA在庫の廃棄手数料</t>
+  </si>
+  <si>
+    <t>FBA保管手数料：</t>
+  </si>
+  <si>
+    <t>FBA長期在庫保管手数料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBA在庫の返金 - 購入者による返品: </t>
+  </si>
+  <si>
+    <t>Service Fee</t>
+  </si>
+  <si>
+    <t>FBA Inventory Fee</t>
+  </si>
+  <si>
+    <t>Adjustment</t>
+  </si>
+  <si>
+    <t>Transaktionsstatus</t>
+  </si>
+  <si>
+    <t>Statut de la transaction</t>
+  </si>
+  <si>
+    <t>Stato della transazione</t>
+  </si>
+  <si>
+    <t>Estado de la transacción</t>
+  </si>
+  <si>
+    <t>Transactiestatus</t>
+  </si>
+  <si>
+    <t>Status transakcji</t>
+  </si>
+  <si>
+    <t>トランザクションのステータス</t>
+  </si>
+  <si>
+    <t>transaction status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Veröffentlicht</t>
+  </si>
+  <si>
+    <t>Verzögert</t>
+  </si>
+  <si>
+    <t>Sorti</t>
+  </si>
+  <si>
+    <t>Différé</t>
+  </si>
+  <si>
+    <t>Emesso</t>
+  </si>
+  <si>
+    <t>Differito</t>
+  </si>
+  <si>
+    <t>Liberada</t>
+  </si>
+  <si>
+    <t>Diferida</t>
+  </si>
+  <si>
+    <t>Effectuée</t>
+  </si>
+  <si>
+    <t>Différée</t>
+  </si>
+  <si>
+    <t>Uitgebracht</t>
+  </si>
+  <si>
+    <t>Uitgesteld</t>
+  </si>
+  <si>
+    <t>Wydano</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Odroczono</t>
+  </si>
+  <si>
+    <t>Släpps</t>
+  </si>
+  <si>
+    <t>Uppskjuten</t>
+  </si>
+  <si>
+    <t>Released</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deferred</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Released</t>
+  </si>
+  <si>
+    <t>Deferred</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
@@ -1816,6 +2057,262 @@
       </c>
       <c r="B80" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A81" t="s">
+        <v>272</v>
+      </c>
+      <c r="B81" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A82" t="s">
+        <v>273</v>
+      </c>
+      <c r="B82" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A83" t="s">
+        <v>269</v>
+      </c>
+      <c r="B83" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A84" t="s">
+        <v>274</v>
+      </c>
+      <c r="B84" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A85" t="s">
+        <v>275</v>
+      </c>
+      <c r="B85" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A86" t="s">
+        <v>270</v>
+      </c>
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A87" t="s">
+        <v>276</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A88" t="s">
+        <v>277</v>
+      </c>
+      <c r="B88" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A89" t="s">
+        <v>278</v>
+      </c>
+      <c r="B89" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A90" t="s">
+        <v>279</v>
+      </c>
+      <c r="B90" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A91" t="s">
+        <v>280</v>
+      </c>
+      <c r="B91" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A92" t="s">
+        <v>281</v>
+      </c>
+      <c r="B92" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A93" t="s">
+        <v>282</v>
+      </c>
+      <c r="B93" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A94" t="s">
+        <v>283</v>
+      </c>
+      <c r="B94" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A95" t="s">
+        <v>284</v>
+      </c>
+      <c r="B95" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A96" t="s">
+        <v>285</v>
+      </c>
+      <c r="B96" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A97" t="s">
+        <v>286</v>
+      </c>
+      <c r="B97" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A98" t="s">
+        <v>287</v>
+      </c>
+      <c r="B98" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A99" t="s">
+        <v>288</v>
+      </c>
+      <c r="B99" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A100" t="s">
+        <v>289</v>
+      </c>
+      <c r="B100" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A101" t="s">
+        <v>290</v>
+      </c>
+      <c r="B101" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A102" t="s">
+        <v>291</v>
+      </c>
+      <c r="B102" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A103" t="s">
+        <v>322</v>
+      </c>
+      <c r="B103" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A104" t="s">
+        <v>315</v>
+      </c>
+      <c r="B104" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A105" t="s">
+        <v>316</v>
+      </c>
+      <c r="B105" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A106" t="s">
+        <v>317</v>
+      </c>
+      <c r="B106" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A107" t="s">
+        <v>318</v>
+      </c>
+      <c r="B107" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A108" t="s">
+        <v>316</v>
+      </c>
+      <c r="B108" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A109" t="s">
+        <v>319</v>
+      </c>
+      <c r="B109" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A110" t="s">
+        <v>320</v>
+      </c>
+      <c r="B110" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A111" t="s">
+        <v>315</v>
+      </c>
+      <c r="B111" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A112" t="s">
+        <v>321</v>
+      </c>
+      <c r="B112" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -1826,8 +2323,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
@@ -2531,6 +3031,198 @@
       </c>
       <c r="B88" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A89" t="s">
+        <v>271</v>
+      </c>
+      <c r="B89" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A90" t="s">
+        <v>307</v>
+      </c>
+      <c r="B90" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A91" t="s">
+        <v>308</v>
+      </c>
+      <c r="B91" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A92" t="s">
+        <v>309</v>
+      </c>
+      <c r="B92" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A93" t="s">
+        <v>310</v>
+      </c>
+      <c r="B93" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A94" t="s">
+        <v>311</v>
+      </c>
+      <c r="B94" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A95" t="s">
+        <v>339</v>
+      </c>
+      <c r="B95" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A96" t="s">
+        <v>340</v>
+      </c>
+      <c r="B96" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A97" t="s">
+        <v>323</v>
+      </c>
+      <c r="B97" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A98" t="s">
+        <v>324</v>
+      </c>
+      <c r="B98" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A99" t="s">
+        <v>325</v>
+      </c>
+      <c r="B99" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A100" t="s">
+        <v>326</v>
+      </c>
+      <c r="B100" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A101" t="s">
+        <v>327</v>
+      </c>
+      <c r="B101" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A102" t="s">
+        <v>328</v>
+      </c>
+      <c r="B102" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A103" t="s">
+        <v>329</v>
+      </c>
+      <c r="B103" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A104" t="s">
+        <v>330</v>
+      </c>
+      <c r="B104" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A105" t="s">
+        <v>331</v>
+      </c>
+      <c r="B105" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A106" t="s">
+        <v>332</v>
+      </c>
+      <c r="B106" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A107" t="s">
+        <v>333</v>
+      </c>
+      <c r="B107" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A108" t="s">
+        <v>334</v>
+      </c>
+      <c r="B108" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A109" t="s">
+        <v>335</v>
+      </c>
+      <c r="B109" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A110" t="s">
+        <v>336</v>
+      </c>
+      <c r="B110" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A111" t="s">
+        <v>337</v>
+      </c>
+      <c r="B111" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A112" t="s">
+        <v>338</v>
+      </c>
+      <c r="B112" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -2541,7 +3233,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
@@ -2798,6 +3490,22 @@
       </c>
       <c r="B32" t="s">
         <v>258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A33" t="s">
+        <v>265</v>
+      </c>
+      <c r="B33" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A34" t="s">
+        <v>267</v>
+      </c>
+      <c r="B34" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
